--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104638_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104638_W20.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6797</v>
+        <v>9.0379</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7182</v>
+        <v>7.9326</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9615</v>
+        <v>1.1052</v>
       </c>
       <c r="G2" t="n">
-        <v>7.6193</v>
+        <v>7.6116</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2221</v>
+        <v>1.2262</v>
       </c>
       <c r="I2" t="n">
-        <v>6.3972</v>
+        <v>6.3855</v>
       </c>
       <c r="J2" t="n">
-        <v>8.1355</v>
+        <v>8.114000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6797</v>
+        <v>1.672</v>
       </c>
       <c r="L2" t="n">
-        <v>6.4558</v>
+        <v>6.442</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5162</v>
+        <v>-0.5023</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0738</v>
+        <v>0.2881</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3436</v>
+        <v>0.4694</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4304</v>
+        <v>4.1443</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5442</v>
+        <v>4.3874</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1138</v>
+        <v>-0.2431</v>
       </c>
       <c r="G3" t="n">
-        <v>2.988</v>
+        <v>2.9824</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.089</v>
       </c>
       <c r="I3" t="n">
-        <v>3.076</v>
+        <v>3.0714</v>
       </c>
       <c r="J3" t="n">
-        <v>5.175</v>
+        <v>5.1478</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7073</v>
+        <v>1.6925</v>
       </c>
       <c r="L3" t="n">
-        <v>3.4678</v>
+        <v>3.4554</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.187</v>
+        <v>-2.1654</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7953</v>
+        <v>-1.7814</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2798</v>
+        <v>0.0057</v>
       </c>
       <c r="T3" t="n">
-        <v>0.248</v>
+        <v>0.1321</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0317</v>
+        <v>-0.1264</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3459</v>
+        <v>1.0373</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3205</v>
+        <v>0.1776</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0253</v>
+        <v>0.8597</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7126</v>
+        <v>1.7158</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3665</v>
+        <v>0.3676</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3461</v>
+        <v>1.3482</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4765</v>
+        <v>2.4614</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1704</v>
+        <v>1.1581</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7639</v>
+        <v>-0.7457</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.153</v>
+        <v>-0.1533</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0484</v>
+        <v>-0.1652</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2014</v>
+        <v>0.0119</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2547</v>
+        <v>0.1271</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3642</v>
+        <v>1.1774</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1096</v>
+        <v>-1.0503</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4274</v>
+        <v>0.4354</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.785</v>
+        <v>-1.7782</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2124</v>
+        <v>2.2136</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4521</v>
+        <v>2.4417</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1346</v>
+        <v>3.1279</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0248</v>
+        <v>-2.0062</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.082</v>
+        <v>-0.2173</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0484</v>
+        <v>-0.214</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0336</v>
+        <v>-0.0033</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9216</v>
+        <v>-0.4199</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5631</v>
+        <v>0.8778</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4847</v>
+        <v>-1.2977</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0489</v>
+        <v>3.0447</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4344</v>
+        <v>-1.4251</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4833</v>
+        <v>4.4697</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6945</v>
+        <v>4.6666</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4085</v>
+        <v>0.3997</v>
       </c>
       <c r="L6" t="n">
-        <v>4.286</v>
+        <v>4.2669</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6457</v>
+        <v>-1.6219</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8429</v>
+        <v>-1.8248</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8363</v>
+        <v>-0.3265</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7289</v>
+        <v>-0.3743</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1074</v>
+        <v>0.0479</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8224</v>
+        <v>-1.899</v>
       </c>
       <c r="E7" t="n">
-        <v>1.671</v>
+        <v>1.5289</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.4934</v>
+        <v>-3.4279</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.8281</v>
+        <v>-3.8187</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.658</v>
+        <v>-2.654</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1701</v>
+        <v>-1.1646</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7325</v>
+        <v>-0.7493</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1701</v>
+        <v>-0.1831</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5625</v>
+        <v>-0.5662</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0956</v>
+        <v>-3.0693</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.4879</v>
+        <v>-2.4709</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4479</v>
+        <v>-0.5356</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0575</v>
+        <v>-0.0585</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5054</v>
+        <v>-0.4771</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2344</v>
+        <v>-3.1019</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4535</v>
+        <v>-2.167</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7809</v>
+        <v>-0.9349</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.9772</v>
+        <v>-3.9655</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7244</v>
+        <v>-2.7174</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2528</v>
+        <v>-1.2481</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6389</v>
+        <v>-0.6541</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8974</v>
+        <v>-0.907</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2585</v>
+        <v>0.253</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3383</v>
+        <v>-3.3114</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.827</v>
+        <v>-1.8103</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3006</v>
+        <v>-0.1835</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8166</v>
+        <v>-0.5113</v>
       </c>
       <c r="U8" t="n">
-        <v>0.516</v>
+        <v>0.3278</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4054</v>
+        <v>-3.4978</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2579</v>
+        <v>-2.5777</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1475</v>
+        <v>-0.9202</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4341</v>
+        <v>-2.4411</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.0893</v>
+        <v>-4.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6552</v>
+        <v>1.6487</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8153</v>
+        <v>-0.8468</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7428</v>
+        <v>-1.7624</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9275</v>
+        <v>0.9156</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6188</v>
+        <v>-1.5943</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.3466</v>
+        <v>-2.3274</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0109</v>
+        <v>-0.107</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.3651</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0708</v>
+        <v>0.2581</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7002</v>
+        <v>-4.6795</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9959</v>
+        <v>-2.9804</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7043</v>
+        <v>-1.6991</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6571</v>
+        <v>-0.2973</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.0492</v>
+        <v>-0.1663</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6079</v>
+        <v>-0.131</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3297</v>
+        <v>0.3906</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3881</v>
+        <v>0.0927</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0584</v>
+        <v>0.2979</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3274</v>
+        <v>-0.6879</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6611</v>
+        <v>-0.259</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6663</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7748</v>
+        <v>0.3414</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2903</v>
+        <v>-0.3207</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4845</v>
+        <v>0.6622</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>-3.8132</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2534</v>
+        <v>-0.7739</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-3.0392</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9291</v>
+        <v>-4.7014</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2601</v>
+        <v>-3.0969</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.669</v>
+        <v>-1.6045</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2948</v>
+        <v>-3.6629</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1615</v>
+        <v>-3.0365</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1333</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4055</v>
+        <v>-0.3647</v>
       </c>
       <c r="K11" t="n">
-        <v>0.107</v>
+        <v>-0.3932</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2985</v>
+        <v>0.0285</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7003</v>
+        <v>-3.2982</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2685</v>
+        <v>-2.6433</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4318</v>
+        <v>-0.6549</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0974</v>
+        <v>-0.7621</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6261</v>
+        <v>-0.3373</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7234</v>
+        <v>-0.4248</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.8243</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7712</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.0531</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.302400000000001</v>
+        <v>-3.952899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>5.213800000000001</v>
+        <v>5.2597</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.516399999999999</v>
+        <v>-9.2128</v>
       </c>
       <c r="G12" t="n">
-        <v>1.604899999999999</v>
+        <v>1.6044</v>
       </c>
       <c r="H12" t="n">
-        <v>-14.4012</v>
+        <v>-14.3625</v>
       </c>
       <c r="I12" t="n">
-        <v>16.0061</v>
+        <v>15.9669</v>
       </c>
       <c r="J12" t="n">
-        <v>20.8227</v>
+        <v>20.6072</v>
       </c>
       <c r="K12" t="n">
-        <v>1.192</v>
+        <v>1.0831</v>
       </c>
       <c r="L12" t="n">
-        <v>19.6307</v>
+        <v>19.5243</v>
       </c>
       <c r="M12" t="n">
-        <v>-19.218</v>
+        <v>-19.0026</v>
       </c>
       <c r="N12" t="n">
-        <v>-15.5934</v>
+        <v>-15.4455</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.6247</v>
+        <v>-3.5573</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1343</v>
+        <v>1.138299999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.8782</v>
+        <v>-15.9342</v>
       </c>
       <c r="R12" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9961</v>
+        <v>-1.6501</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.7522</v>
+        <v>-2.3956</v>
       </c>
       <c r="U12" t="n">
-        <v>0.756</v>
+        <v>0.7457</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.045199999999999</v>
+        <v>-5.0454</v>
       </c>
       <c r="W12" t="n">
-        <v>3.0214</v>
+        <v>2.9827</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.066700000000001</v>
+        <v>-8.0282</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.674799999999999</v>
+        <v>9.6334</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2838</v>
+        <v>7.7</v>
       </c>
       <c r="F13" t="n">
-        <v>2.391</v>
+        <v>1.9334</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5211</v>
+        <v>5.5016</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7562</v>
+        <v>4.7453</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7649</v>
+        <v>0.7563</v>
       </c>
       <c r="J13" t="n">
-        <v>6.0159</v>
+        <v>5.9706</v>
       </c>
       <c r="K13" t="n">
-        <v>5.0565</v>
+        <v>5.0332</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9594</v>
+        <v>0.9375</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4948</v>
+        <v>-0.469</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5412</v>
+        <v>1.5171</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3297</v>
+        <v>0.1438</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8709</v>
+        <v>1.3733</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W13" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5386</v>
+        <v>4.8776</v>
       </c>
       <c r="E14" t="n">
-        <v>3.713</v>
+        <v>3.9309</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8256</v>
+        <v>0.9467</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8151</v>
+        <v>1.8206</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3433</v>
+        <v>1.3468</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8804</v>
+        <v>2.8648</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8009</v>
+        <v>1.7926</v>
       </c>
       <c r="L14" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0653</v>
+        <v>-1.0442</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4966</v>
+        <v>0.8294</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2601</v>
+        <v>-0.0234</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7567</v>
+        <v>0.8528</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. TAVARES</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.327</v>
+        <v>2.2957</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2566</v>
+        <v>0.2049</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9297</v>
+        <v>2.0908</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0537</v>
+        <v>-1.8344</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9278</v>
+        <v>-0.0573</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8742</v>
+        <v>-1.7771</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5617</v>
+        <v>-1.0074</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3378</v>
+        <v>0.0582</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2239</v>
+        <v>-1.0656</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.508</v>
+        <v>-0.827</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4099</v>
+        <v>-0.1155</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0981</v>
+        <v>-0.7114</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>2.5039</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1126</v>
+        <v>0.5367</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0294</v>
+        <v>0.1228</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0832</v>
+        <v>0.4138</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9320000000000001</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>E. TAVARES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0105</v>
+        <v>0.5122</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3567</v>
+        <v>0.9402</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3672</v>
+        <v>-0.428</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8327</v>
+        <v>1.0641</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0548</v>
+        <v>1.9245</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7779</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9806</v>
+        <v>2.5504</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07240000000000001</v>
+        <v>2.327</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.053</v>
+        <v>0.2234</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8521</v>
+        <v>-1.4863</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1272</v>
+        <v>-0.4025</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7249</v>
+        <v>-1.0838</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4952</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7446</v>
+        <v>1.2904</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4688</v>
+        <v>0.736</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2758</v>
+        <v>0.5543</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6639</v>
+        <v>0.5058</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5352</v>
+        <v>-1.2699</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8713</v>
+        <v>1.7758</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5476</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9235</v>
+        <v>1.3272</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3759</v>
+        <v>-1.2417</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1843</v>
+        <v>1.5269</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8139</v>
+        <v>0.7822</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3705</v>
+        <v>0.7447</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6368</v>
+        <v>-1.4414</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1096</v>
+        <v>0.5451</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7463</v>
+        <v>-1.9865</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5039</v>
+        <v>0.2382</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5777</v>
+        <v>-0.2442</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0738</v>
+        <v>0.4824</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>1.5479</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5002</v>
+        <v>0.3172</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1984</v>
+        <v>1.0539</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6985</v>
+        <v>-0.7367</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0605</v>
+        <v>0.5447</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.9247</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.38</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4848</v>
+        <v>1.1748</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4475</v>
+        <v>0.8101</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.3647</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5453</v>
+        <v>-0.6301</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5831</v>
+        <v>0.1146</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.7447</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.361</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.361</v>
-      </c>
       <c r="S18" t="n">
-        <v>0.2674</v>
+        <v>0.1579</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2994</v>
+        <v>0.1067</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0321</v>
+        <v>0.0512</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7071</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4822</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.621</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8254</v>
+        <v>0.5171</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3248</v>
+        <v>-1.1381</v>
       </c>
       <c r="G19" t="n">
-        <v>0.078</v>
+        <v>-0.4144</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3334</v>
+        <v>1.4474</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2554</v>
+        <v>-1.8618</v>
       </c>
       <c r="J19" t="n">
-        <v>1.546</v>
+        <v>0.8446</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7997</v>
+        <v>0.8446</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7463</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.468</v>
+        <v>-1.259</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5337</v>
+        <v>0.6028</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0017</v>
+        <v>-1.8618</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6293</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2683</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7601</v>
+        <v>-0.3856</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8347</v>
+        <v>-0.2788</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0747</v>
+        <v>-0.1067</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5425</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.744</v>
+        <v>-0.6633</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5288</v>
+        <v>-0.1775</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2728</v>
+        <v>-0.4858</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.42</v>
+        <v>-0.0629</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4458</v>
+        <v>0.859</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8658</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8485</v>
+        <v>1.4711</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8485</v>
+        <v>1.4339</v>
       </c>
       <c r="L20" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1.534</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.5749</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.9592000000000001</v>
+      </c>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="n">
-        <v>-1.2685</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.5973000000000001</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-1.8658</v>
-      </c>
-      <c r="P20" t="n">
-        <v>-0.9073</v>
-      </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5093</v>
+        <v>0.1021</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2782</v>
+        <v>-0.0536</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2311</v>
+        <v>0.1557</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0927</v>
+        <v>-0.7025</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>-0.2292</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7543</v>
+        <v>-1.7392</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0931</v>
+        <v>0.1782</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8474</v>
+        <v>-1.9174</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4467</v>
+        <v>-1.4546</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3432</v>
+        <v>-0.3555</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1035</v>
+        <v>-1.0991</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6231</v>
+        <v>1.5978</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4289</v>
+        <v>0.4062</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1941</v>
+        <v>1.1916</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.0698</v>
+        <v>-3.0524</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.2976</v>
+        <v>-2.2907</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1461</v>
+        <v>0.1707</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3297</v>
+        <v>-0.2115</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4757</v>
+        <v>0.3823</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8394</v>
+        <v>-2.0622</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0622</v>
+        <v>-1.2199</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7772</v>
+        <v>-0.8423</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0302</v>
+        <v>-3.0344</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2266</v>
+        <v>1.2182</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.2568</v>
+        <v>-4.2527</v>
       </c>
       <c r="J22" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0427</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0075</v>
+        <v>0.989</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0993</v>
+        <v>-3.0772</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.3185</v>
+        <v>-3.3064</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2323</v>
+        <v>0.021</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0484</v>
+        <v>-0.1652</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2806</v>
+        <v>0.1862</v>
       </c>
       <c r="V22" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4874</v>
+        <v>-3.2731</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7225</v>
+        <v>-1.625</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7649</v>
+        <v>-1.6481</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6869</v>
+        <v>-1.679</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5468</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2337</v>
+        <v>-2.2329</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6256</v>
+        <v>1.6155</v>
       </c>
       <c r="K23" t="n">
-        <v>0.658</v>
+        <v>0.655</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.3125</v>
+        <v>-3.2945</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.2012</v>
+        <v>-3.1934</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5302</v>
+        <v>-0.3194</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6261</v>
+        <v>-0.5089</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0959</v>
+        <v>0.1895</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0865</v>
+        <v>-3.9025</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1258</v>
+        <v>-1.0203</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9607</v>
+        <v>-2.8822</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1434</v>
+        <v>-2.1412</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4315</v>
+        <v>0.4281</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5749</v>
+        <v>-2.5693</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3592</v>
+        <v>0.3508</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3219</v>
+        <v>0.3135</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5026</v>
+        <v>-2.492</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.6122</v>
+        <v>-2.6066</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7597</v>
+        <v>-0.5808</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.302499999999999</v>
+        <v>5.880599999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>9.516299999999999</v>
+        <v>9.2126</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.2139</v>
+        <v>-3.3319</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.6049</v>
+        <v>-1.604400000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>14.4013</v>
+        <v>14.3623</v>
       </c>
       <c r="I25" t="n">
-        <v>-16.0063</v>
+        <v>-15.9668</v>
       </c>
       <c r="J25" t="n">
-        <v>19.218</v>
+        <v>19.0026</v>
       </c>
       <c r="K25" t="n">
-        <v>15.5935</v>
+        <v>15.4455</v>
       </c>
       <c r="L25" t="n">
-        <v>3.6245</v>
+        <v>3.5571</v>
       </c>
       <c r="M25" t="n">
-        <v>-20.823</v>
+        <v>-20.6071</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1921</v>
+        <v>-1.0831</v>
       </c>
       <c r="O25" t="n">
-        <v>-19.6307</v>
+        <v>-19.524</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.134</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q25" t="n">
-        <v>-17.0125</v>
+        <v>-17.0724</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8782</v>
+        <v>15.9341</v>
       </c>
       <c r="S25" t="n">
-        <v>1.9962</v>
+        <v>3.577699999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7561</v>
+        <v>-0.7458</v>
       </c>
       <c r="U25" t="n">
-        <v>2.7521</v>
+        <v>4.3235</v>
       </c>
       <c r="V25" t="n">
-        <v>5.045400000000001</v>
+        <v>5.045500000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>8.066799999999999</v>
+        <v>8.028400000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.0214</v>
+        <v>-2.9828</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104638_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104638_W20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.0392</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-8.0282</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104638_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-2.9828</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
